--- a/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SPRINGFIELD SCHOOL</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.92205</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.237981</v>
-      </c>
-      <c r="I2" t="n">
-        <v>356</v>
-      </c>
-      <c r="J2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.92205</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.237981</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>32002 VIRGEN DEL CARMEN / 389 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.92351</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.23511000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>607</v>
-      </c>
-      <c r="J3" t="n">
-        <v>39</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.92351</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.23511</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>001 DR. CARLOS SHOWING FERRARI</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.932700000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.2452</v>
-      </c>
-      <c r="I4" t="n">
-        <v>405</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.9327</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.2452</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>002</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.92665</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.23903</v>
-      </c>
-      <c r="I5" t="n">
-        <v>215</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.92665</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.23903</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>003 LAURITA VICUÑA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.926869999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.2366</v>
-      </c>
-      <c r="I6" t="n">
-        <v>336</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.92687</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.2366</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>005 FRAY MARTINCITO DE PORRES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.93923</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.24876</v>
-      </c>
-      <c r="I7" t="n">
-        <v>204</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.93923</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.24876</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>006 INMACULADA NIÑA MARIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.921139999999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.23614999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>206</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.92114</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.23615</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>108 MARIA MONTESSORI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.92633</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.24145</v>
-      </c>
-      <c r="I9" t="n">
-        <v>238</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.92633</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.24145</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>141</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.92136</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.24369</v>
-      </c>
-      <c r="I10" t="n">
-        <v>215</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.92136</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.24369</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>32004 SAN PEDRO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.931509999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.24948999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1656</v>
-      </c>
-      <c r="J11" t="n">
-        <v>70</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.93151</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.24949</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>32008 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.93524</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.2469</v>
-      </c>
-      <c r="I12" t="n">
-        <v>741</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.93524</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.2469</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>32011 HERMILIO VALDIZAN</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.92657</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.23953</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1359</v>
-      </c>
-      <c r="J13" t="n">
-        <v>52</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.92657</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.23953</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>32013 PEDRO SANCHEZ GAVIDIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.938207999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.25082500000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>894</v>
-      </c>
-      <c r="J14" t="n">
-        <v>47</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.938208</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.250825</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>32814 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-9.92122</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.23631</v>
-      </c>
-      <c r="I15" t="n">
-        <v>463</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-9.92122</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.23631</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>32046 DANIEL ALOMIA ROBLES</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-9.93323</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.24905</v>
-      </c>
-      <c r="I16" t="n">
-        <v>763</v>
-      </c>
-      <c r="J16" t="n">
-        <v>34</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-9.93323</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.24905</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>33012</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-9.92699</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.24915</v>
-      </c>
-      <c r="I17" t="n">
-        <v>260</v>
-      </c>
-      <c r="J17" t="n">
-        <v>13</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-9.92699</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.24915</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>33073</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-9.926548</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.245918</v>
-      </c>
-      <c r="I18" t="n">
-        <v>230</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-9.926548</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.245918</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>33074 HEROES DE JACTAY</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-9.921427</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.243585</v>
-      </c>
-      <c r="I19" t="n">
-        <v>938</v>
-      </c>
-      <c r="J19" t="n">
-        <v>42</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-9.921427</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.243585</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>33129</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-9.923400000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.24590000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>255</v>
-      </c>
-      <c r="J20" t="n">
-        <v>13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-9.9234</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.2459</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>33130</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-9.915469999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.23961</v>
-      </c>
-      <c r="I21" t="n">
-        <v>424</v>
-      </c>
-      <c r="J21" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-9.91547</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.23961</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-9.91727</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.24189</v>
-      </c>
-      <c r="I22" t="n">
-        <v>534</v>
-      </c>
-      <c r="J22" t="n">
-        <v>26</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-9.91727</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.24189</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>ILLATHUPA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-9.924860000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.24356</v>
-      </c>
-      <c r="I23" t="n">
-        <v>881</v>
-      </c>
-      <c r="J23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-9.92486</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.24356</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>32232 JUANA MORENO / JUANA MORENO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-9.928660000000001</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.23778</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1376</v>
-      </c>
-      <c r="J24" t="n">
-        <v>65</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-9.92866</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.23778</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>GRAN UNIDAD ESCOLAR LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-9.927910000000001</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.24231</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4218</v>
-      </c>
-      <c r="J25" t="n">
-        <v>180</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-9.92791</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.24231</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>MILAGRO DE FATIMA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-9.92184</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.23801</v>
-      </c>
-      <c r="I26" t="n">
-        <v>916</v>
-      </c>
-      <c r="J26" t="n">
-        <v>48</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-9.92184</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.23801</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-9.93186</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.24924</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1905</v>
-      </c>
-      <c r="J27" t="n">
-        <v>96</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-9.93186</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.24924</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>ECLECIAL LA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-9.92778</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.24533</v>
-      </c>
-      <c r="I28" t="n">
-        <v>630</v>
-      </c>
-      <c r="J28" t="n">
-        <v>47</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-9.92778</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.24533</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-9.932449999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.23881</v>
-      </c>
-      <c r="I29" t="n">
-        <v>318</v>
-      </c>
-      <c r="J29" t="n">
-        <v>28</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-9.93245</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.23881</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SEMINARIO SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-9.93112</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.24263000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>607</v>
-      </c>
-      <c r="J30" t="n">
-        <v>37</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-9.93112</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.24263</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>SANTA ELIZABETH</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-9.93108</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.23739999999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>344</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-9.93108</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.2374</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>AMADEUS MOZART</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-9.929169999999999</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.23569999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>345</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-9.92917</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.2357</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>EL PRINCIPITO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-9.92413</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.2353</v>
-      </c>
-      <c r="I33" t="n">
-        <v>297</v>
-      </c>
-      <c r="J33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-9.92413</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.2353</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-9.92421</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.24223000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>544</v>
-      </c>
-      <c r="J34" t="n">
-        <v>22</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-9.92421</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.24223</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>MATUSITA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-9.92431</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.23542</v>
-      </c>
-      <c r="I35" t="n">
-        <v>285</v>
-      </c>
-      <c r="J35" t="n">
-        <v>13</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-9.92431</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.23542</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-9.9349343</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.24156309999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>67</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-9.9349343</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.2415631</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SANTO DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-9.926729999999999</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.23845</v>
-      </c>
-      <c r="I37" t="n">
-        <v>201</v>
-      </c>
-      <c r="J37" t="n">
-        <v>10</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-9.92673</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.23845</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>PILLKO MARKA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-9.92511</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.24256</v>
-      </c>
-      <c r="I38" t="n">
-        <v>200</v>
-      </c>
-      <c r="J38" t="n">
-        <v>14</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-9.92511</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.24256</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>32126 MARIA CAUSA DE NUESTRA ALEGRIA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-9.925800000000001</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.1682</v>
-      </c>
-      <c r="I39" t="n">
-        <v>208</v>
-      </c>
-      <c r="J39" t="n">
-        <v>13</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-9.9258</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.1682</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SANTA ROSA DE MAYOBAMBA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-9.749672</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.091831</v>
-      </c>
-      <c r="I40" t="n">
-        <v>367</v>
-      </c>
-      <c r="J40" t="n">
-        <v>27</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-9.749672</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.091831</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>32692</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-9.774749</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-75.915729</v>
-      </c>
-      <c r="I41" t="n">
-        <v>203</v>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-9.774749</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-75.915729</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>32082</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-9.751799999999999</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.2645</v>
-      </c>
-      <c r="I42" t="n">
-        <v>300</v>
-      </c>
-      <c r="J42" t="n">
-        <v>27</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-9.7518</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.2645</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>32844</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-9.770799999999999</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.20740000000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>216</v>
-      </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-9.7708</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.2074</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>33134</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-9.749337000000001</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.217839</v>
-      </c>
-      <c r="I44" t="n">
-        <v>335</v>
-      </c>
-      <c r="J44" t="n">
-        <v>18</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-9.749337</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.217839</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>GABRIEL AGUILAR NALVARTE</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-9.980600000000001</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.2841</v>
-      </c>
-      <c r="I45" t="n">
-        <v>421</v>
-      </c>
-      <c r="J45" t="n">
-        <v>29</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-9.9806</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.2841</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>32124 ALEJO HUARAUYA PALOMINO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-9.8546</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.1981</v>
-      </c>
-      <c r="I46" t="n">
-        <v>295</v>
-      </c>
-      <c r="J46" t="n">
-        <v>22</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-9.8546</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.1981</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>32630</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-9.792790999999999</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.354732</v>
-      </c>
-      <c r="I47" t="n">
-        <v>229</v>
-      </c>
-      <c r="J47" t="n">
-        <v>16</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-9.792791</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.354732</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>32743 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-9.792350000000001</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.311671</v>
-      </c>
-      <c r="I48" t="n">
-        <v>234</v>
-      </c>
-      <c r="J48" t="n">
-        <v>19</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-9.79235</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.311671</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>ANDRES A. CACERES</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-10.005</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.4682</v>
-      </c>
-      <c r="I49" t="n">
-        <v>244</v>
-      </c>
-      <c r="J49" t="n">
-        <v>24</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-10.005</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.4682</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SAN PABLO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-9.93404</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.24393999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>270</v>
-      </c>
-      <c r="J50" t="n">
-        <v>21</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-9.93404</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.24394</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>SAN VICENTE DE LA BARQUERA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-9.929449999999999</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.23699000000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>899</v>
-      </c>
-      <c r="J51" t="n">
-        <v>60</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-9.92945</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.23699</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>NIÑO DIVINO JESUS</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-9.930149999999999</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.23560000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>252</v>
-      </c>
-      <c r="J52" t="n">
-        <v>24</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-9.93015</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.2356</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>ALBERTO BARTON THOMPSON</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-9.932079999999999</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.24447000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>211</v>
-      </c>
-      <c r="J53" t="n">
-        <v>25</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-9.93208</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.24447</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>ISAAC NEWTON</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-9.92658</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.23833</v>
-      </c>
-      <c r="I54" t="n">
-        <v>592</v>
-      </c>
-      <c r="J54" t="n">
-        <v>40</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-9.92658</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.23833</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-9.93366</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.24538</v>
-      </c>
-      <c r="I55" t="n">
-        <v>210</v>
-      </c>
-      <c r="J55" t="n">
-        <v>20</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-9.93366</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.24538</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>PERUANA ALEMANA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-9.93458</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.24525</v>
-      </c>
-      <c r="I56" t="n">
-        <v>285</v>
-      </c>
-      <c r="J56" t="n">
-        <v>24</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-9.93458</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.24525</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>COAR HUANUCO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-9.920463</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.30939600000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>267</v>
-      </c>
-      <c r="J57" t="n">
-        <v>31</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-9.920463</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.309396</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>VON NEUMANN - CRESPO CASTILLO</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-9.92567</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-76.2427</v>
-      </c>
-      <c r="I58" t="n">
-        <v>464</v>
-      </c>
-      <c r="J58" t="n">
-        <v>22</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-9.92567</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-76.2427</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>LA DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-9.928190000000001</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-76.23863</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1154</v>
-      </c>
-      <c r="J59" t="n">
-        <v>46</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-9.92819</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-76.23863</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>VON NEUMANN</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-9.927210000000001</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-76.23838000000001</v>
-      </c>
-      <c r="I60" t="n">
-        <v>651</v>
-      </c>
-      <c r="J60" t="n">
-        <v>14</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-9.92721</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-76.23838</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>LA SALLE SCHOOL</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-9.93121</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.24395</v>
-      </c>
-      <c r="I61" t="n">
-        <v>492</v>
-      </c>
-      <c r="J61" t="n">
-        <v>22</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-9.93121</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.24395</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-9.933719999999999</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-76.24330999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1601</v>
-      </c>
-      <c r="J62" t="n">
-        <v>57</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-9.93372</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-76.24331</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>189817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SPRINGFIELD SCHOOL</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.92205</t>
+          <t>-9.92136</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.237981</t>
+          <t>-76.24369</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>190726</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32002 VIRGEN DEL CARMEN / 389 VIRGEN DEL CARMEN</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.92351</t>
+          <t>-9.9349343</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.23511</t>
+          <t>-76.2415631</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>189718</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>001 DR. CARLOS SHOWING FERRARI</t>
+          <t>SANTO DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.9327</t>
+          <t>-9.92673</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.2452</t>
+          <t>-76.23845</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>189737</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>108 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.92665</t>
+          <t>-9.92633</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.23903</t>
+          <t>-76.24145</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>189742</t>
+          <t>190175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>003 LAURITA VICUÑA</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.92687</t>
+          <t>-9.926548</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.2366</t>
+          <t>-76.245918</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>189761</t>
+          <t>190156</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>005 FRAY MARTINCITO DE PORRES</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.93923</t>
+          <t>-9.92699</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.24876</t>
+          <t>-76.24915</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>190199</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>006 INMACULADA NIÑA MARIA</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.92114</t>
+          <t>-9.9234</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.23615</t>
+          <t>-76.2459</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>189803</t>
+          <t>190665</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108 MARIA MONTESSORI</t>
+          <t>MATUSITA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.92633</t>
+          <t>-9.92431</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.24145</t>
+          <t>-76.23542</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>189817</t>
+          <t>191170</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>32126 MARIA CAUSA DE NUESTRA ALEGRIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.92136</t>
+          <t>-9.9258</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.24369</t>
+          <t>-76.1682</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>189916</t>
+          <t>190910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32004 SAN PEDRO</t>
+          <t>PILLKO MARKA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.93151</t>
+          <t>-9.92511</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.24949</t>
+          <t>-76.24256</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>189921</t>
+          <t>832097</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32008 SEÑOR DE LOS MILAGROS</t>
+          <t>VON NEUMANN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.93524</t>
+          <t>-9.92721</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.2469</t>
+          <t>-76.23838</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>651</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>189935</t>
+          <t>192004</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32011 HERMILIO VALDIZAN</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.92657</t>
+          <t>-9.774749</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.23953</t>
+          <t>-75.915729</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>189940</t>
+          <t>189742</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>32013 PEDRO SANCHEZ GAVIDIA</t>
+          <t>003 LAURITA VICUÑA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.938208</t>
+          <t>-9.92687</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.250825</t>
+          <t>-76.2366</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>190038</t>
+          <t>190566</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>32814 MIGUEL GRAU SEMINARIO</t>
+          <t>EL PRINCIPITO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.92122</t>
+          <t>-9.92413</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.23631</t>
+          <t>-76.2353</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>190142</t>
+          <t>193857</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32046 DANIEL ALOMIA ROBLES</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.93323</t>
+          <t>-9.792791</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.24905</t>
+          <t>-76.354732</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>190156</t>
+          <t>192607</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.92699</t>
+          <t>-9.7708</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.24915</t>
+          <t>-76.2074</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>190175</t>
+          <t>190203</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33073</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.926548</t>
+          <t>-9.91547</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.245918</t>
+          <t>-76.23961</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>190180</t>
+          <t>192626</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33074 HEROES DE JACTAY</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.921427</t>
+          <t>-9.749337</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.243585</t>
+          <t>-76.217839</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>190199</t>
+          <t>190335</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>GRAN UNIDAD ESCOLAR LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.9234</t>
+          <t>-9.92791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.2459</t>
+          <t>-76.24231</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>180</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>190203</t>
+          <t>190038</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>32814 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.91547</t>
+          <t>-9.92122</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.23961</t>
+          <t>-76.23631</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>190217</t>
+          <t>193956</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JOSE GALVEZ EGUSQUIZA</t>
+          <t>32743 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.91727</t>
+          <t>-9.79235</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.24189</t>
+          <t>-76.311671</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>190284</t>
+          <t>189718</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ILLATHUPA</t>
+          <t>001 DR. CARLOS SHOWING FERRARI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.92486</t>
+          <t>-9.9327</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.24356</t>
+          <t>-76.2452</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>190298</t>
+          <t>190496</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>32232 JUANA MORENO / JUANA MORENO</t>
+          <t>AMADEUS MOZART</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.92866</t>
+          <t>-9.92917</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.23778</t>
+          <t>-76.2357</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>190335</t>
+          <t>622928</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GRAN UNIDAD ESCOLAR LEONCIO PRADO</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.92791</t>
+          <t>-9.93366</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.24231</t>
+          <t>-76.24538</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>190364</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MILAGRO DE FATIMA</t>
+          <t>SPRINGFIELD SCHOOL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.92184</t>
+          <t>-9.92205</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.23801</t>
+          <t>-76.237981</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,42 +2051,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>190383</t>
+          <t>549278</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>SAN PABLO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.93186</t>
+          <t>-9.93404</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.24924</t>
+          <t>-76.24394</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>190444</t>
+          <t>190477</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ECLECIAL LA INMACULADA CONCEPCION</t>
+          <t>SANTA ELIZABETH</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.92778</t>
+          <t>-9.93108</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.24533</t>
+          <t>-76.2374</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>190458</t>
+          <t>190646</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.93245</t>
+          <t>-9.92421</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.23881</t>
+          <t>-76.24223</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>544</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>190463</t>
+          <t>193838</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEMINARIO SAN LUIS GONZAGA</t>
+          <t>32124 ALEJO HUARAUYA PALOMINO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.93112</t>
+          <t>-9.8546</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.24263</t>
+          <t>-76.1981</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,27 +2299,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>190477</t>
+          <t>830791</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SANTA ELIZABETH</t>
+          <t>VON NEUMANN - CRESPO CASTILLO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.93108</t>
+          <t>-9.92567</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.2374</t>
+          <t>-76.2427</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>464</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,42 +2361,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>190496</t>
+          <t>843519</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AMADEUS MOZART</t>
+          <t>LA SALLE SCHOOL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.92917</t>
+          <t>-9.93121</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.2357</t>
+          <t>-76.24395</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>194423</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EL PRINCIPITO</t>
+          <t>ANDRES A. CACERES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.92413</t>
+          <t>-10.005</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.2353</t>
+          <t>-76.4682</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>190646</t>
+          <t>559390</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>NIÑO DIVINO JESUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.92421</t>
+          <t>-9.93015</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.24223</t>
+          <t>-76.2356</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>190665</t>
+          <t>743242</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MATUSITA</t>
+          <t>PERUANA ALEMANA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.92431</t>
+          <t>-9.93458</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.23542</t>
+          <t>-76.24525</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,42 +2609,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>190726</t>
+          <t>622669</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>ALBERTO BARTON THOMPSON</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.9349343</t>
+          <t>-9.93208</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.2415631</t>
+          <t>-76.24447</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>190825</t>
+          <t>190217</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO SAVIO</t>
+          <t>JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.92673</t>
+          <t>-9.91727</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.23845</t>
+          <t>-76.24189</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>534</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>190910</t>
+          <t>191919</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PILLKO MARKA</t>
+          <t>SANTA ROSA DE MAYOBAMBA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.92511</t>
+          <t>-9.749672</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.24256</t>
+          <t>-76.091831</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>191170</t>
+          <t>192513</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>32126 MARIA CAUSA DE NUESTRA ALEGRIA</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.9258</t>
+          <t>-9.7518</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.1682</t>
+          <t>-76.2645</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>191919</t>
+          <t>190458</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE MAYOBAMBA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.749672</t>
+          <t>-9.93245</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.091831</t>
+          <t>-76.23881</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>192004</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>GABRIEL AGUILAR NALVARTE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.774749</t>
+          <t>-9.9806</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.915729</t>
+          <t>-76.2841</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>192513</t>
+          <t>784671</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>COAR HUANUCO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.7518</t>
+          <t>-9.920463</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.2645</t>
+          <t>-76.309396</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>192607</t>
+          <t>189921</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>32008 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.7708</t>
+          <t>-9.93524</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.2074</t>
+          <t>-76.2469</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>741</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>192626</t>
+          <t>190142</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>32046 DANIEL ALOMIA ROBLES</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.749337</t>
+          <t>-9.93323</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.217839</t>
+          <t>-76.24905</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>763</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,42 +3167,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>193490</t>
+          <t>190463</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GABRIEL AGUILAR NALVARTE</t>
+          <t>SEMINARIO SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.9806</t>
+          <t>-9.93112</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.2841</t>
+          <t>-76.24263</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>607</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>193838</t>
+          <t>189704</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>32124 ALEJO HUARAUYA PALOMINO</t>
+          <t>32002 VIRGEN DEL CARMEN / 389 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.8546</t>
+          <t>-9.92351</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.1981</t>
+          <t>-76.23511</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>607</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>193857</t>
+          <t>622706</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.792791</t>
+          <t>-9.92658</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.354732</t>
+          <t>-76.23833</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>592</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>193956</t>
+          <t>190180</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>32743 SANTA ROSA DE LIMA</t>
+          <t>33074 HEROES DE JACTAY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.79235</t>
+          <t>-9.921427</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.311671</t>
+          <t>-76.243585</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>194423</t>
+          <t>831229</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ANDRES A. CACERES</t>
+          <t>LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-10.005</t>
+          <t>-9.92819</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.4682</t>
+          <t>-76.23863</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,42 +3477,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>549278</t>
+          <t>189940</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>32013 PEDRO SANCHEZ GAVIDIA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-9.93404</t>
+          <t>-9.938208</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.24394</t>
+          <t>-76.250825</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>894</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>552973</t>
+          <t>190444</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE LA BARQUERA</t>
+          <t>ECLECIAL LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-9.92945</t>
+          <t>-9.92778</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.23699</t>
+          <t>-76.24533</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>630</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>559390</t>
+          <t>190364</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NIÑO DIVINO JESUS</t>
+          <t>MILAGRO DE FATIMA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-9.93015</t>
+          <t>-9.92184</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.2356</t>
+          <t>-76.23801</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>916</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>622669</t>
+          <t>189935</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ALBERTO BARTON THOMPSON</t>
+          <t>32011 HERMILIO VALDIZAN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-9.93208</t>
+          <t>-9.92657</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.24447</t>
+          <t>-76.23953</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>622706</t>
+          <t>860311</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-9.92658</t>
+          <t>-9.93372</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.23833</t>
+          <t>-76.24331</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>622928</t>
+          <t>190284</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>ILLATHUPA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-9.93366</t>
+          <t>-9.92486</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.24538</t>
+          <t>-76.24356</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>881</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>743242</t>
+          <t>552973</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PERUANA ALEMANA</t>
+          <t>SAN VICENTE DE LA BARQUERA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-9.93458</t>
+          <t>-9.92945</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.24525</t>
+          <t>-76.23699</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>899</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>784671</t>
+          <t>190298</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>COAR HUANUCO</t>
+          <t>32232 JUANA MORENO / JUANA MORENO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-9.920463</t>
+          <t>-9.92866</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.309396</t>
+          <t>-76.23778</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>830791</t>
+          <t>189916</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VON NEUMANN - CRESPO CASTILLO</t>
+          <t>32004 SAN PEDRO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-9.92567</t>
+          <t>-9.93151</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.2427</t>
+          <t>-76.24949</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>831229</t>
+          <t>189737</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LA DIVINA MISERICORDIA</t>
+          <t>002</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-9.92819</t>
+          <t>-9.92665</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.23863</t>
+          <t>-76.23903</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,42 +4097,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>832097</t>
+          <t>189761</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VON NEUMANN</t>
+          <t>005 FRAY MARTINCITO DE PORRES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-9.92721</t>
+          <t>-9.93923</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.23838</t>
+          <t>-76.24876</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,37 +4159,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>843519</t>
+          <t>189775</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA SALLE SCHOOL</t>
+          <t>006 INMACULADA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-9.93121</t>
+          <t>-9.92114</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.24395</t>
+          <t>-76.23615</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>860311</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-9.93372</t>
+          <t>-9.93186</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.24331</t>
+          <t>-76.24924</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">

--- a/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>189817</t>
+          <t>860311</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.92136</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.24369</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-9.93372</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.24331</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>190726</t>
+          <t>843519</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>LA SALLE SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.9349343</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.2415631</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-9.93121</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.24395</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>190825</t>
+          <t>832097</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO SAVIO</t>
+          <t>VON NEUMANN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.92673</t>
+          <t>651</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.23845</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-9.92721</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.23838</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>189803</t>
+          <t>831229</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108 MARIA MONTESSORI</t>
+          <t>LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.92633</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.24145</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-9.92819</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.23863</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>190175</t>
+          <t>830791</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33073</t>
+          <t>VON NEUMANN - CRESPO CASTILLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.926548</t>
+          <t>464</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.245918</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-9.92567</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.2427</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>190156</t>
+          <t>784671</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>COAR HUANUCO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.92699</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.24915</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-9.920463</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.309396</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>190199</t>
+          <t>743242</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>PERUANA ALEMANA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.9234</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.2459</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-9.93458</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.24525</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>190665</t>
+          <t>622928</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MATUSITA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.92431</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.23542</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-9.93366</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.24538</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>191170</t>
+          <t>622706</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32126 MARIA CAUSA DE NUESTRA ALEGRIA</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.9258</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.1682</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-9.92658</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.23833</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>190910</t>
+          <t>622669</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PILLKO MARKA</t>
+          <t>ALBERTO BARTON THOMPSON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.92511</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.24256</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-9.93208</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.24447</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>832097</t>
+          <t>559390</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VON NEUMANN</t>
+          <t>NIÑO DIVINO JESUS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.92721</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.23838</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>-9.93015</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.2356</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>192004</t>
+          <t>552973</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>SAN VICENTE DE LA BARQUERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.774749</t>
+          <t>899</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.915729</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-9.92945</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.23699</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,42 +1245,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>189742</t>
+          <t>549278</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>003 LAURITA VICUÑA</t>
+          <t>SAN PABLO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.92687</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.2366</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-9.93404</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.24394</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>194423</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EL PRINCIPITO</t>
+          <t>ANDRES A. CACERES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.92413</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.2353</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-10.005</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.4682</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>193857</t>
+          <t>193956</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>32743 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.792791</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.354732</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-9.79235</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.311671</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>192607</t>
+          <t>193857</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.7708</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.2074</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-9.792791</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.354732</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>190203</t>
+          <t>193838</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>32124 ALEJO HUARAUYA PALOMINO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.91547</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.23961</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>-9.8546</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.1981</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>192626</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>GABRIEL AGUILAR NALVARTE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.749337</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.217839</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-9.9806</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.2841</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>190335</t>
+          <t>192626</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GRAN UNIDAD ESCOLAR LEONCIO PRADO</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.92791</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.24231</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>-9.749337</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>-76.217839</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>190038</t>
+          <t>192607</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32814 MIGUEL GRAU SEMINARIO</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.92122</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.23631</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>-9.7708</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.2074</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>193956</t>
+          <t>192513</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>32743 SANTA ROSA DE LIMA</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.79235</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.311671</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-9.7518</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.2645</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>189718</t>
+          <t>192004</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>001 DR. CARLOS SHOWING FERRARI</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.9327</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.2452</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-9.774749</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.915729</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>190496</t>
+          <t>191919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AMADEUS MOZART</t>
+          <t>SANTA ROSA DE MAYOBAMBA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.92917</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.2357</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-9.749672</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.091831</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>622928</t>
+          <t>191170</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>32126 MARIA CAUSA DE NUESTRA ALEGRIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.93366</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.24538</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-9.9258</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.1682</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>190910</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SPRINGFIELD SCHOOL</t>
+          <t>PILLKO MARKA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.92205</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.237981</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-9.92511</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.24256</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>549278</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>SANTO DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.93404</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.24394</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-9.92673</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.23845</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>190477</t>
+          <t>190726</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTA ELIZABETH</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.93108</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.2374</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-9.9349343</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.2415631</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>190646</t>
+          <t>190665</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>MATUSITA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.92421</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.24223</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>-9.92431</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.23542</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>193838</t>
+          <t>190646</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>32124 ALEJO HUARAUYA PALOMINO</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.8546</t>
+          <t>544</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.1981</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-9.92421</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.24223</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>830791</t>
+          <t>190566</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VON NEUMANN - CRESPO CASTILLO</t>
+          <t>EL PRINCIPITO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.92567</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.2427</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>-9.92413</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.2353</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,42 +2361,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>843519</t>
+          <t>190496</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LA SALLE SCHOOL</t>
+          <t>AMADEUS MOZART</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.93121</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.24395</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>-9.92917</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.2357</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>194423</t>
+          <t>190477</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ANDRES A. CACERES</t>
+          <t>SANTA ELIZABETH</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-10.005</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.4682</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-9.93108</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.2374</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,42 +2485,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>559390</t>
+          <t>190463</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NIÑO DIVINO JESUS</t>
+          <t>SEMINARIO SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.93015</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.2356</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-9.93112</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.24263</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>743242</t>
+          <t>190458</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PERUANA ALEMANA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.93458</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.24525</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-9.93245</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.23881</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>622669</t>
+          <t>190444</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALBERTO BARTON THOMPSON</t>
+          <t>ECLECIAL LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.93208</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.24447</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-9.92778</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.24533</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>190217</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JOSE GALVEZ EGUSQUIZA</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.91727</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.24189</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-9.93186</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.24924</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>191919</t>
+          <t>190364</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE MAYOBAMBA</t>
+          <t>MILAGRO DE FATIMA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.749672</t>
+          <t>916</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.091831</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-9.92184</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.23801</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>192513</t>
+          <t>190335</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>GRAN UNIDAD ESCOLAR LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.7518</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.2645</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-9.92791</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.24231</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>190458</t>
+          <t>190298</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>32232 JUANA MORENO / JUANA MORENO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.93245</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.23881</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-9.92866</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.23778</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>193490</t>
+          <t>190284</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GABRIEL AGUILAR NALVARTE</t>
+          <t>ILLATHUPA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.9806</t>
+          <t>881</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.2841</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-9.92486</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.24356</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>784671</t>
+          <t>190217</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>COAR HUANUCO</t>
+          <t>JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.920463</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.309396</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-9.91727</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.24189</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>189921</t>
+          <t>190203</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>32008 SEÑOR DE LOS MILAGROS</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.93524</t>
+          <t>424</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.2469</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>-9.91547</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.23961</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>190142</t>
+          <t>190199</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>32046 DANIEL ALOMIA ROBLES</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.93323</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.24905</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>-9.9234</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.2459</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,42 +3167,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>190463</t>
+          <t>190180</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SEMINARIO SAN LUIS GONZAGA</t>
+          <t>33074 HEROES DE JACTAY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.93112</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.24263</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>-9.921427</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.243585</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>190175</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>32002 VIRGEN DEL CARMEN / 389 VIRGEN DEL CARMEN</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.92351</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.23511</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>-9.926548</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.245918</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>622706</t>
+          <t>190156</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.92658</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.23833</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>-9.92699</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.24915</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>190180</t>
+          <t>190142</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>33074 HEROES DE JACTAY</t>
+          <t>32046 DANIEL ALOMIA ROBLES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.921427</t>
+          <t>763</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.243585</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-9.93323</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.24905</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>831229</t>
+          <t>190038</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LA DIVINA MISERICORDIA</t>
+          <t>32814 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-9.92819</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.23863</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>-9.92122</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.23631</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>-9.938208</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>-76.250825</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>190444</t>
+          <t>189935</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ECLECIAL LA INMACULADA CONCEPCION</t>
+          <t>32011 HERMILIO VALDIZAN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-9.92778</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.24533</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>-9.92657</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.23953</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>190364</t>
+          <t>189921</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MILAGRO DE FATIMA</t>
+          <t>32008 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-9.92184</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.23801</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>-9.93524</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.2469</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>189935</t>
+          <t>189916</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>32011 HERMILIO VALDIZAN</t>
+          <t>32004 SAN PEDRO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-9.92657</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.23953</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>-9.93151</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.24949</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,42 +3725,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>860311</t>
+          <t>189817</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-9.93372</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.24331</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>-9.92136</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-76.24369</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>190284</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ILLATHUPA</t>
+          <t>108 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-9.92486</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.24356</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>-9.92633</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.24145</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>552973</t>
+          <t>189775</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE LA BARQUERA</t>
+          <t>006 INMACULADA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-9.92945</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.23699</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>-9.92114</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.23615</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>190298</t>
+          <t>189761</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>32232 JUANA MORENO / JUANA MORENO</t>
+          <t>005 FRAY MARTINCITO DE PORRES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-9.92866</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.23778</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>-9.93923</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-76.24876</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>189916</t>
+          <t>189742</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>32004 SAN PEDRO</t>
+          <t>003 LAURITA VICUÑA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-9.93151</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.24949</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>-9.92687</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-76.2366</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4045,22 +4045,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>-9.92665</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>-76.23903</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,42 +4097,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>189761</t>
+          <t>189718</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>005 FRAY MARTINCITO DE PORRES</t>
+          <t>001 DR. CARLOS SHOWING FERRARI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-9.93923</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.24876</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-9.9327</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.2452</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>189704</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>006 INMACULADA NIÑA MARIA</t>
+          <t>32002 VIRGEN DEL CARMEN / 389 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-9.92114</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.23615</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-9.92351</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.23511</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>190383</t>
+          <t>082171</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>SPRINGFIELD SCHOOL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-9.93186</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.24924</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>-9.92205</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-76.237981</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
